--- a/resources/variable_schema_data_household_template.xlsx
+++ b/resources/variable_schema_data_household_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE472A36-A5E5-4EE2-A22A-D2265CE685D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC05E618-253F-440E-83F2-BB60EB80AE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9476" uniqueCount="1970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9476" uniqueCount="1971">
   <si>
     <t>rule_type</t>
   </si>
@@ -5930,6 +5930,9 @@
   </si>
   <si>
     <t>مدة المقابلة بالدقائق</t>
+  </si>
+  <si>
+    <t>datetime</t>
   </si>
 </sst>
 </file>
@@ -7253,7 +7256,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>1970</v>
       </c>
       <c r="G24" t="b">
         <v>0</v>
@@ -7282,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>1970</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>

--- a/resources/variable_schema_data_household_template.xlsx
+++ b/resources/variable_schema_data_household_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A457B890-FC0F-4726-84D8-3E35D348AB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E363EDF8-ACB4-4885-86FB-966535AEF947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="1987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="1991">
   <si>
     <t>rule_type</t>
   </si>
@@ -5953,18 +5953,12 @@
     <t>num_children_30_59m</t>
   </si>
   <si>
-    <t>linked_roster_num_children_6_29m,num_children_6_29m</t>
-  </si>
-  <si>
     <t xml:space="preserve">Original Roster children 6-29 months </t>
   </si>
   <si>
     <t xml:space="preserve">Original Roster children 30-59 months </t>
   </si>
   <si>
-    <t>linked_roster_num_children_30_59m,num_children_30_59m</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linked Roster children 6-29 months </t>
   </si>
   <si>
@@ -5981,6 +5975,24 @@
   </si>
   <si>
     <t>قائمة الأطفال المرتبطين من عمر 30 إلى 59 شهر</t>
+  </si>
+  <si>
+    <t>linked_roster_age_30_59m,age_30_59m</t>
+  </si>
+  <si>
+    <t>linked_roster_age_6_29m</t>
+  </si>
+  <si>
+    <t>linked_roster_age_30_59m</t>
+  </si>
+  <si>
+    <t>age_30_59m</t>
+  </si>
+  <si>
+    <t>age_6_29m</t>
+  </si>
+  <si>
+    <t>linked_roster_age_6_29m,age_6_29m</t>
   </si>
 </sst>
 </file>
@@ -7728,16 +7740,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>1977</v>
+        <v>1990</v>
       </c>
       <c r="L38" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="M38" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="N38" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -7757,16 +7769,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="s">
+        <v>1985</v>
+      </c>
+      <c r="L39" t="s">
         <v>1980</v>
       </c>
-      <c r="L39" t="s">
-        <v>1982</v>
-      </c>
       <c r="M39" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="N39" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -7786,16 +7798,16 @@
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="L40" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="M40" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="N40" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -7815,16 +7827,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>1976</v>
+        <v>1988</v>
       </c>
       <c r="L41" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="M41" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="N41" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -7844,16 +7856,16 @@
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>1971</v>
+        <v>1986</v>
       </c>
       <c r="L42" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="M42" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="N42" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -7873,16 +7885,16 @@
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>1972</v>
+        <v>1987</v>
       </c>
       <c r="L43" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="M43" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="N43" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">

--- a/resources/variable_schema_data_household_template.xlsx
+++ b/resources/variable_schema_data_household_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E363EDF8-ACB4-4885-86FB-966535AEF947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E8B7AA-5819-4FCC-94D5-84058209E1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resources/variable_schema_data_household_template.xlsx
+++ b/resources/variable_schema_data_household_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E8B7AA-5819-4FCC-94D5-84058209E1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F70DBA-23C3-4D50-AE94-F2B6FBA8389F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="1991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9550" uniqueCount="2007">
   <si>
     <t>rule_type</t>
   </si>
@@ -5993,6 +5993,54 @@
   </si>
   <si>
     <t>linked_roster_age_6_29m,age_6_29m</t>
+  </si>
+  <si>
+    <t>linked_person_time</t>
+  </si>
+  <si>
+    <t>linked_person_time_under5</t>
+  </si>
+  <si>
+    <t>linked_person_time_male</t>
+  </si>
+  <si>
+    <t>linked_person_time_female</t>
+  </si>
+  <si>
+    <t>Linked Person Time</t>
+  </si>
+  <si>
+    <t>Linked Person Time Under5</t>
+  </si>
+  <si>
+    <t>Linked Person Time Male</t>
+  </si>
+  <si>
+    <t>Linked Person Time Female</t>
+  </si>
+  <si>
+    <t>وقت الشخص المرتبط</t>
+  </si>
+  <si>
+    <t>وقت الشخص المرتبط دون سن الخامسة</t>
+  </si>
+  <si>
+    <t>وقت الشخص المرتبط من الذكور</t>
+  </si>
+  <si>
+    <t>وقت الشخص المرتبط من الإناث</t>
+  </si>
+  <si>
+    <t>Temps de la personne liée</t>
+  </si>
+  <si>
+    <t>Temps de la personne liée (moins de 5 ans)</t>
+  </si>
+  <si>
+    <t>Temps de la personne liée (homme)</t>
+  </si>
+  <si>
+    <t>Temps de la personne liée (femme)</t>
   </si>
 </sst>
 </file>
@@ -6034,7 +6082,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6493,7 +6551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S793"/>
+  <dimension ref="A1:S797"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
@@ -41401,54 +41459,185 @@
         <v>1961</v>
       </c>
     </row>
+    <row r="794" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A794" t="s">
+        <v>1</v>
+      </c>
+      <c r="B794" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D794">
+        <v>0</v>
+      </c>
+      <c r="E794" t="s">
+        <v>48</v>
+      </c>
+      <c r="F794" t="s">
+        <v>66</v>
+      </c>
+      <c r="G794" t="b">
+        <v>0</v>
+      </c>
+      <c r="J794" t="s">
+        <v>1991</v>
+      </c>
+      <c r="L794" t="s">
+        <v>1995</v>
+      </c>
+      <c r="M794" t="s">
+        <v>2003</v>
+      </c>
+      <c r="N794" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="795" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A795" t="s">
+        <v>1</v>
+      </c>
+      <c r="B795" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D795">
+        <v>0</v>
+      </c>
+      <c r="E795" t="s">
+        <v>48</v>
+      </c>
+      <c r="F795" t="s">
+        <v>66</v>
+      </c>
+      <c r="G795" t="b">
+        <v>0</v>
+      </c>
+      <c r="J795" t="s">
+        <v>1992</v>
+      </c>
+      <c r="L795" t="s">
+        <v>1996</v>
+      </c>
+      <c r="M795" t="s">
+        <v>2004</v>
+      </c>
+      <c r="N795" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="796" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A796" t="s">
+        <v>1</v>
+      </c>
+      <c r="B796" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D796">
+        <v>0</v>
+      </c>
+      <c r="E796" t="s">
+        <v>48</v>
+      </c>
+      <c r="F796" t="s">
+        <v>66</v>
+      </c>
+      <c r="G796" t="b">
+        <v>0</v>
+      </c>
+      <c r="J796" t="s">
+        <v>1993</v>
+      </c>
+      <c r="L796" t="s">
+        <v>1997</v>
+      </c>
+      <c r="M796" t="s">
+        <v>2005</v>
+      </c>
+      <c r="N796" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="797" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A797" t="s">
+        <v>1</v>
+      </c>
+      <c r="B797" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D797">
+        <v>0</v>
+      </c>
+      <c r="E797" t="s">
+        <v>48</v>
+      </c>
+      <c r="F797" t="s">
+        <v>66</v>
+      </c>
+      <c r="G797" t="b">
+        <v>0</v>
+      </c>
+      <c r="J797" t="s">
+        <v>1994</v>
+      </c>
+      <c r="L797" t="s">
+        <v>1998</v>
+      </c>
+      <c r="M797" t="s">
+        <v>2006</v>
+      </c>
+      <c r="N797" t="s">
+        <v>2002</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B749:B793">
-    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
+  <conditionalFormatting sqref="B749:B797">
+    <cfRule type="duplicateValues" dxfId="16" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C743:C746 C749:C751">
-    <cfRule type="duplicateValues" dxfId="14" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C753:C755">
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C757:C759 C761:C763">
+    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J749:J760">
     <cfRule type="duplicateValues" dxfId="12" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J749:J760">
-    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J761:J763">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J764:J765">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J779:J781 J784">
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J782">
     <cfRule type="duplicateValues" dxfId="8" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J782">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J783">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J785:J786">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J788">
     <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J788">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  <conditionalFormatting sqref="J789">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J789">
+  <conditionalFormatting sqref="J791">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J791">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J792">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P729:P741">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J794:J797">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/resources/variable_schema_data_household_template.xlsx
+++ b/resources/variable_schema_data_household_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C494B8-6871-4BB6-ACA9-91B02C8A4479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D9823B-F4A3-4D13-948C-63174DA3034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9624" uniqueCount="2046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9648" uniqueCount="2060">
   <si>
     <t>rule_type</t>
   </si>
@@ -6158,6 +6158,48 @@
   </si>
   <si>
     <t>linked_roster_5plus,num_5plus</t>
+  </si>
+  <si>
+    <t>num_births</t>
+  </si>
+  <si>
+    <t>original_num_births</t>
+  </si>
+  <si>
+    <t>linked_num_births</t>
+  </si>
+  <si>
+    <t>Number of Births</t>
+  </si>
+  <si>
+    <t>Original Number of Births</t>
+  </si>
+  <si>
+    <t>Linked Number of Births</t>
+  </si>
+  <si>
+    <t>Nombre de naissances</t>
+  </si>
+  <si>
+    <t>Nombre initial de naissances</t>
+  </si>
+  <si>
+    <t>Nombre de naissances liées</t>
+  </si>
+  <si>
+    <t>عدد المواليد</t>
+  </si>
+  <si>
+    <t>العدد الأصلي للمواليد</t>
+  </si>
+  <si>
+    <t>عدد المواليد المرتبطين</t>
+  </si>
+  <si>
+    <t>linked_roster_birth,num_births</t>
+  </si>
+  <si>
+    <t>linked_roster_birth</t>
   </si>
 </sst>
 </file>
@@ -6199,7 +6241,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6668,7 +6720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S810"/>
+  <dimension ref="A1:S813"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
@@ -40947,7 +40999,7 @@
         <v>1</v>
       </c>
       <c r="B777" t="s">
-        <v>1821</v>
+        <v>2046</v>
       </c>
       <c r="D777">
         <v>0</v>
@@ -40962,16 +41014,16 @@
         <v>0</v>
       </c>
       <c r="J777" t="s">
-        <v>1822</v>
+        <v>2058</v>
       </c>
       <c r="L777" t="s">
-        <v>1823</v>
+        <v>2049</v>
       </c>
       <c r="M777" t="s">
-        <v>1824</v>
+        <v>2052</v>
       </c>
       <c r="N777" t="s">
-        <v>1825</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="778" spans="1:17" x14ac:dyDescent="0.25">
@@ -40979,7 +41031,7 @@
         <v>1</v>
       </c>
       <c r="B778" t="s">
-        <v>1826</v>
+        <v>2047</v>
       </c>
       <c r="D778">
         <v>0</v>
@@ -40994,16 +41046,16 @@
         <v>0</v>
       </c>
       <c r="J778" t="s">
-        <v>1827</v>
+        <v>2046</v>
       </c>
       <c r="L778" t="s">
-        <v>1828</v>
+        <v>2050</v>
       </c>
       <c r="M778" t="s">
-        <v>1829</v>
+        <v>2053</v>
       </c>
       <c r="N778" t="s">
-        <v>1830</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="779" spans="1:17" x14ac:dyDescent="0.25">
@@ -41011,7 +41063,7 @@
         <v>1</v>
       </c>
       <c r="B779" t="s">
-        <v>1831</v>
+        <v>2048</v>
       </c>
       <c r="D779">
         <v>0</v>
@@ -41026,16 +41078,16 @@
         <v>0</v>
       </c>
       <c r="J779" t="s">
-        <v>1832</v>
+        <v>2059</v>
       </c>
       <c r="L779" t="s">
-        <v>1833</v>
+        <v>2051</v>
       </c>
       <c r="M779" t="s">
-        <v>1834</v>
+        <v>2054</v>
       </c>
       <c r="N779" t="s">
-        <v>1835</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="780" spans="1:17" x14ac:dyDescent="0.25">
@@ -41043,7 +41095,7 @@
         <v>1</v>
       </c>
       <c r="B780" t="s">
-        <v>1836</v>
+        <v>1821</v>
       </c>
       <c r="D780">
         <v>0</v>
@@ -41058,16 +41110,16 @@
         <v>0</v>
       </c>
       <c r="J780" t="s">
-        <v>1837</v>
+        <v>1822</v>
       </c>
       <c r="L780" t="s">
-        <v>1838</v>
+        <v>1823</v>
       </c>
       <c r="M780" t="s">
-        <v>1839</v>
+        <v>1824</v>
       </c>
       <c r="N780" t="s">
-        <v>1840</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="781" spans="1:17" x14ac:dyDescent="0.25">
@@ -41075,7 +41127,7 @@
         <v>1</v>
       </c>
       <c r="B781" t="s">
-        <v>1841</v>
+        <v>1826</v>
       </c>
       <c r="D781">
         <v>0</v>
@@ -41090,16 +41142,16 @@
         <v>0</v>
       </c>
       <c r="J781" t="s">
-        <v>1836</v>
+        <v>1827</v>
       </c>
       <c r="L781" t="s">
-        <v>1842</v>
+        <v>1828</v>
       </c>
       <c r="M781" t="s">
-        <v>1843</v>
+        <v>1829</v>
       </c>
       <c r="N781" t="s">
-        <v>1844</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="782" spans="1:17" x14ac:dyDescent="0.25">
@@ -41107,7 +41159,7 @@
         <v>1</v>
       </c>
       <c r="B782" t="s">
-        <v>1845</v>
+        <v>1831</v>
       </c>
       <c r="D782">
         <v>0</v>
@@ -41122,16 +41174,16 @@
         <v>0</v>
       </c>
       <c r="J782" t="s">
-        <v>1846</v>
+        <v>1832</v>
       </c>
       <c r="L782" t="s">
-        <v>1847</v>
+        <v>1833</v>
       </c>
       <c r="M782" t="s">
-        <v>1848</v>
+        <v>1834</v>
       </c>
       <c r="N782" t="s">
-        <v>1849</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="783" spans="1:17" x14ac:dyDescent="0.25">
@@ -41139,7 +41191,7 @@
         <v>1</v>
       </c>
       <c r="B783" t="s">
-        <v>1850</v>
+        <v>1836</v>
       </c>
       <c r="D783">
         <v>0</v>
@@ -41154,16 +41206,16 @@
         <v>0</v>
       </c>
       <c r="J783" t="s">
-        <v>1851</v>
+        <v>1837</v>
       </c>
       <c r="L783" t="s">
-        <v>1852</v>
+        <v>1838</v>
       </c>
       <c r="M783" t="s">
-        <v>1853</v>
+        <v>1839</v>
       </c>
       <c r="N783" t="s">
-        <v>1854</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="784" spans="1:17" x14ac:dyDescent="0.25">
@@ -41171,7 +41223,7 @@
         <v>1</v>
       </c>
       <c r="B784" t="s">
-        <v>1855</v>
+        <v>1841</v>
       </c>
       <c r="D784">
         <v>0</v>
@@ -41186,16 +41238,16 @@
         <v>0</v>
       </c>
       <c r="J784" t="s">
-        <v>1850</v>
+        <v>1836</v>
       </c>
       <c r="L784" t="s">
-        <v>1856</v>
+        <v>1842</v>
       </c>
       <c r="M784" t="s">
-        <v>1857</v>
+        <v>1843</v>
       </c>
       <c r="N784" t="s">
-        <v>1858</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="785" spans="1:14" x14ac:dyDescent="0.25">
@@ -41203,7 +41255,7 @@
         <v>1</v>
       </c>
       <c r="B785" t="s">
-        <v>1859</v>
+        <v>1845</v>
       </c>
       <c r="D785">
         <v>0</v>
@@ -41218,16 +41270,16 @@
         <v>0</v>
       </c>
       <c r="J785" t="s">
-        <v>1860</v>
+        <v>1846</v>
       </c>
       <c r="L785" t="s">
-        <v>1861</v>
+        <v>1847</v>
       </c>
       <c r="M785" t="s">
-        <v>1862</v>
+        <v>1848</v>
       </c>
       <c r="N785" t="s">
-        <v>1863</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="786" spans="1:14" x14ac:dyDescent="0.25">
@@ -41235,7 +41287,7 @@
         <v>1</v>
       </c>
       <c r="B786" t="s">
-        <v>1864</v>
+        <v>1850</v>
       </c>
       <c r="D786">
         <v>0</v>
@@ -41250,16 +41302,16 @@
         <v>0</v>
       </c>
       <c r="J786" t="s">
-        <v>1865</v>
+        <v>1851</v>
       </c>
       <c r="L786" t="s">
-        <v>1866</v>
+        <v>1852</v>
       </c>
       <c r="M786" t="s">
-        <v>1867</v>
+        <v>1853</v>
       </c>
       <c r="N786" t="s">
-        <v>1868</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="787" spans="1:14" x14ac:dyDescent="0.25">
@@ -41267,7 +41319,7 @@
         <v>1</v>
       </c>
       <c r="B787" t="s">
-        <v>1869</v>
+        <v>1855</v>
       </c>
       <c r="D787">
         <v>0</v>
@@ -41282,16 +41334,16 @@
         <v>0</v>
       </c>
       <c r="J787" t="s">
-        <v>1864</v>
+        <v>1850</v>
       </c>
       <c r="L787" t="s">
-        <v>1870</v>
+        <v>1856</v>
       </c>
       <c r="M787" t="s">
-        <v>1871</v>
+        <v>1857</v>
       </c>
       <c r="N787" t="s">
-        <v>1872</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="788" spans="1:14" x14ac:dyDescent="0.25">
@@ -41299,7 +41351,7 @@
         <v>1</v>
       </c>
       <c r="B788" t="s">
-        <v>1873</v>
+        <v>1859</v>
       </c>
       <c r="D788">
         <v>0</v>
@@ -41314,16 +41366,16 @@
         <v>0</v>
       </c>
       <c r="J788" t="s">
-        <v>1874</v>
+        <v>1860</v>
       </c>
       <c r="L788" t="s">
-        <v>1875</v>
+        <v>1861</v>
       </c>
       <c r="M788" t="s">
-        <v>1876</v>
+        <v>1862</v>
       </c>
       <c r="N788" t="s">
-        <v>1877</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="789" spans="1:14" x14ac:dyDescent="0.25">
@@ -41331,7 +41383,7 @@
         <v>1</v>
       </c>
       <c r="B789" t="s">
-        <v>1878</v>
+        <v>1864</v>
       </c>
       <c r="D789">
         <v>0</v>
@@ -41346,16 +41398,16 @@
         <v>0</v>
       </c>
       <c r="J789" t="s">
-        <v>1879</v>
+        <v>1865</v>
       </c>
       <c r="L789" t="s">
-        <v>1880</v>
+        <v>1866</v>
       </c>
       <c r="M789" t="s">
-        <v>1881</v>
+        <v>1867</v>
       </c>
       <c r="N789" t="s">
-        <v>1882</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="790" spans="1:14" x14ac:dyDescent="0.25">
@@ -41363,7 +41415,7 @@
         <v>1</v>
       </c>
       <c r="B790" t="s">
-        <v>1883</v>
+        <v>1869</v>
       </c>
       <c r="D790">
         <v>0</v>
@@ -41378,16 +41430,16 @@
         <v>0</v>
       </c>
       <c r="J790" t="s">
-        <v>1878</v>
+        <v>1864</v>
       </c>
       <c r="L790" t="s">
-        <v>1884</v>
+        <v>1870</v>
       </c>
       <c r="M790" t="s">
-        <v>1885</v>
+        <v>1871</v>
       </c>
       <c r="N790" t="s">
-        <v>1886</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="791" spans="1:14" x14ac:dyDescent="0.25">
@@ -41395,7 +41447,7 @@
         <v>1</v>
       </c>
       <c r="B791" t="s">
-        <v>1887</v>
+        <v>1873</v>
       </c>
       <c r="D791">
         <v>0</v>
@@ -41410,16 +41462,16 @@
         <v>0</v>
       </c>
       <c r="J791" t="s">
-        <v>1888</v>
+        <v>1874</v>
       </c>
       <c r="L791" t="s">
-        <v>1889</v>
+        <v>1875</v>
       </c>
       <c r="M791" t="s">
-        <v>1890</v>
+        <v>1876</v>
       </c>
       <c r="N791" t="s">
-        <v>1891</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="792" spans="1:14" x14ac:dyDescent="0.25">
@@ -41427,7 +41479,7 @@
         <v>1</v>
       </c>
       <c r="B792" t="s">
-        <v>1892</v>
+        <v>1878</v>
       </c>
       <c r="D792">
         <v>0</v>
@@ -41442,16 +41494,16 @@
         <v>0</v>
       </c>
       <c r="J792" t="s">
-        <v>1893</v>
+        <v>1879</v>
       </c>
       <c r="L792" t="s">
-        <v>1894</v>
+        <v>1880</v>
       </c>
       <c r="M792" t="s">
-        <v>1895</v>
+        <v>1881</v>
       </c>
       <c r="N792" t="s">
-        <v>1896</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="793" spans="1:14" x14ac:dyDescent="0.25">
@@ -41459,7 +41511,7 @@
         <v>1</v>
       </c>
       <c r="B793" t="s">
-        <v>1897</v>
+        <v>1883</v>
       </c>
       <c r="D793">
         <v>0</v>
@@ -41474,16 +41526,16 @@
         <v>0</v>
       </c>
       <c r="J793" t="s">
-        <v>1892</v>
+        <v>1878</v>
       </c>
       <c r="L793" t="s">
-        <v>1898</v>
+        <v>1884</v>
       </c>
       <c r="M793" t="s">
-        <v>1899</v>
+        <v>1885</v>
       </c>
       <c r="N793" t="s">
-        <v>1900</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="794" spans="1:14" x14ac:dyDescent="0.25">
@@ -41491,7 +41543,7 @@
         <v>1</v>
       </c>
       <c r="B794" t="s">
-        <v>1901</v>
+        <v>1887</v>
       </c>
       <c r="D794">
         <v>0</v>
@@ -41506,16 +41558,16 @@
         <v>0</v>
       </c>
       <c r="J794" t="s">
-        <v>1902</v>
+        <v>1888</v>
       </c>
       <c r="L794" t="s">
-        <v>1903</v>
+        <v>1889</v>
       </c>
       <c r="M794" t="s">
-        <v>1904</v>
+        <v>1890</v>
       </c>
       <c r="N794" t="s">
-        <v>1905</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="795" spans="1:14" x14ac:dyDescent="0.25">
@@ -41523,7 +41575,7 @@
         <v>1</v>
       </c>
       <c r="B795" t="s">
-        <v>1906</v>
+        <v>1892</v>
       </c>
       <c r="D795">
         <v>0</v>
@@ -41538,16 +41590,16 @@
         <v>0</v>
       </c>
       <c r="J795" t="s">
-        <v>1907</v>
+        <v>1893</v>
       </c>
       <c r="L795" t="s">
-        <v>1908</v>
+        <v>1894</v>
       </c>
       <c r="M795" t="s">
-        <v>1909</v>
+        <v>1895</v>
       </c>
       <c r="N795" t="s">
-        <v>1910</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="796" spans="1:14" x14ac:dyDescent="0.25">
@@ -41555,7 +41607,7 @@
         <v>1</v>
       </c>
       <c r="B796" t="s">
-        <v>1911</v>
+        <v>1897</v>
       </c>
       <c r="D796">
         <v>0</v>
@@ -41570,16 +41622,16 @@
         <v>0</v>
       </c>
       <c r="J796" t="s">
-        <v>1906</v>
+        <v>1892</v>
       </c>
       <c r="L796" t="s">
-        <v>1912</v>
+        <v>1898</v>
       </c>
       <c r="M796" t="s">
-        <v>1913</v>
+        <v>1899</v>
       </c>
       <c r="N796" t="s">
-        <v>1914</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="797" spans="1:14" x14ac:dyDescent="0.25">
@@ -41587,7 +41639,7 @@
         <v>1</v>
       </c>
       <c r="B797" t="s">
-        <v>1915</v>
+        <v>1901</v>
       </c>
       <c r="D797">
         <v>0</v>
@@ -41602,16 +41654,16 @@
         <v>0</v>
       </c>
       <c r="J797" t="s">
-        <v>1916</v>
+        <v>1902</v>
       </c>
       <c r="L797" t="s">
-        <v>1917</v>
+        <v>1903</v>
       </c>
       <c r="M797" t="s">
-        <v>1918</v>
+        <v>1904</v>
       </c>
       <c r="N797" t="s">
-        <v>1919</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="798" spans="1:14" x14ac:dyDescent="0.25">
@@ -41619,7 +41671,7 @@
         <v>1</v>
       </c>
       <c r="B798" t="s">
-        <v>1920</v>
+        <v>1906</v>
       </c>
       <c r="D798">
         <v>0</v>
@@ -41634,16 +41686,16 @@
         <v>0</v>
       </c>
       <c r="J798" t="s">
-        <v>1921</v>
+        <v>1907</v>
       </c>
       <c r="L798" t="s">
-        <v>1922</v>
+        <v>1908</v>
       </c>
       <c r="M798" t="s">
-        <v>1923</v>
+        <v>1909</v>
       </c>
       <c r="N798" t="s">
-        <v>1924</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="799" spans="1:14" x14ac:dyDescent="0.25">
@@ -41651,7 +41703,7 @@
         <v>1</v>
       </c>
       <c r="B799" t="s">
-        <v>1925</v>
+        <v>1911</v>
       </c>
       <c r="D799">
         <v>0</v>
@@ -41666,16 +41718,16 @@
         <v>0</v>
       </c>
       <c r="J799" t="s">
-        <v>1920</v>
+        <v>1906</v>
       </c>
       <c r="L799" t="s">
-        <v>1926</v>
+        <v>1912</v>
       </c>
       <c r="M799" t="s">
-        <v>1927</v>
+        <v>1913</v>
       </c>
       <c r="N799" t="s">
-        <v>1928</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="800" spans="1:14" x14ac:dyDescent="0.25">
@@ -41683,7 +41735,7 @@
         <v>1</v>
       </c>
       <c r="B800" t="s">
-        <v>1929</v>
+        <v>1915</v>
       </c>
       <c r="D800">
         <v>0</v>
@@ -41698,16 +41750,16 @@
         <v>0</v>
       </c>
       <c r="J800" t="s">
-        <v>1930</v>
+        <v>1916</v>
       </c>
       <c r="L800" t="s">
-        <v>1931</v>
+        <v>1917</v>
       </c>
       <c r="M800" t="s">
-        <v>1932</v>
+        <v>1918</v>
       </c>
       <c r="N800" t="s">
-        <v>1933</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="801" spans="1:14" x14ac:dyDescent="0.25">
@@ -41715,7 +41767,7 @@
         <v>1</v>
       </c>
       <c r="B801" t="s">
-        <v>1934</v>
+        <v>1920</v>
       </c>
       <c r="D801">
         <v>0</v>
@@ -41730,16 +41782,16 @@
         <v>0</v>
       </c>
       <c r="J801" t="s">
-        <v>1935</v>
+        <v>1921</v>
       </c>
       <c r="L801" t="s">
-        <v>1936</v>
+        <v>1922</v>
       </c>
       <c r="M801" t="s">
-        <v>1937</v>
+        <v>1923</v>
       </c>
       <c r="N801" t="s">
-        <v>1938</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="802" spans="1:14" x14ac:dyDescent="0.25">
@@ -41747,7 +41799,7 @@
         <v>1</v>
       </c>
       <c r="B802" t="s">
-        <v>1939</v>
+        <v>1925</v>
       </c>
       <c r="D802">
         <v>0</v>
@@ -41762,16 +41814,16 @@
         <v>0</v>
       </c>
       <c r="J802" t="s">
-        <v>1934</v>
+        <v>1920</v>
       </c>
       <c r="L802" t="s">
-        <v>1940</v>
+        <v>1926</v>
       </c>
       <c r="M802" t="s">
-        <v>1941</v>
+        <v>1927</v>
       </c>
       <c r="N802" t="s">
-        <v>1942</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="803" spans="1:14" x14ac:dyDescent="0.25">
@@ -41779,7 +41831,7 @@
         <v>1</v>
       </c>
       <c r="B803" t="s">
-        <v>1943</v>
+        <v>1929</v>
       </c>
       <c r="D803">
         <v>0</v>
@@ -41794,16 +41846,16 @@
         <v>0</v>
       </c>
       <c r="J803" t="s">
-        <v>1944</v>
+        <v>1930</v>
       </c>
       <c r="L803" t="s">
-        <v>1945</v>
+        <v>1931</v>
       </c>
       <c r="M803" t="s">
-        <v>1946</v>
+        <v>1932</v>
       </c>
       <c r="N803" t="s">
-        <v>1947</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="804" spans="1:14" x14ac:dyDescent="0.25">
@@ -41811,7 +41863,7 @@
         <v>1</v>
       </c>
       <c r="B804" t="s">
-        <v>1948</v>
+        <v>1934</v>
       </c>
       <c r="D804">
         <v>0</v>
@@ -41826,16 +41878,16 @@
         <v>0</v>
       </c>
       <c r="J804" t="s">
-        <v>1949</v>
+        <v>1935</v>
       </c>
       <c r="L804" t="s">
-        <v>1950</v>
+        <v>1936</v>
       </c>
       <c r="M804" t="s">
-        <v>1951</v>
+        <v>1937</v>
       </c>
       <c r="N804" t="s">
-        <v>1952</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="805" spans="1:14" x14ac:dyDescent="0.25">
@@ -41843,7 +41895,7 @@
         <v>1</v>
       </c>
       <c r="B805" t="s">
-        <v>1953</v>
+        <v>1939</v>
       </c>
       <c r="D805">
         <v>0</v>
@@ -41858,16 +41910,16 @@
         <v>0</v>
       </c>
       <c r="J805" t="s">
-        <v>1948</v>
+        <v>1934</v>
       </c>
       <c r="L805" t="s">
-        <v>1954</v>
+        <v>1940</v>
       </c>
       <c r="M805" t="s">
-        <v>1955</v>
+        <v>1941</v>
       </c>
       <c r="N805" t="s">
-        <v>1956</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="806" spans="1:14" x14ac:dyDescent="0.25">
@@ -41875,7 +41927,7 @@
         <v>1</v>
       </c>
       <c r="B806" t="s">
-        <v>1957</v>
+        <v>1943</v>
       </c>
       <c r="D806">
         <v>0</v>
@@ -41890,16 +41942,16 @@
         <v>0</v>
       </c>
       <c r="J806" t="s">
-        <v>1958</v>
+        <v>1944</v>
       </c>
       <c r="L806" t="s">
-        <v>1959</v>
+        <v>1945</v>
       </c>
       <c r="M806" t="s">
-        <v>1960</v>
+        <v>1946</v>
       </c>
       <c r="N806" t="s">
-        <v>1961</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="807" spans="1:14" x14ac:dyDescent="0.25">
@@ -41907,7 +41959,7 @@
         <v>1</v>
       </c>
       <c r="B807" t="s">
-        <v>1991</v>
+        <v>1948</v>
       </c>
       <c r="D807">
         <v>0</v>
@@ -41916,22 +41968,22 @@
         <v>48</v>
       </c>
       <c r="F807" t="s">
-        <v>66</v>
+        <v>371</v>
       </c>
       <c r="G807" t="b">
         <v>0</v>
       </c>
       <c r="J807" t="s">
-        <v>1991</v>
+        <v>1949</v>
       </c>
       <c r="L807" t="s">
-        <v>1995</v>
+        <v>1950</v>
       </c>
       <c r="M807" t="s">
-        <v>2003</v>
+        <v>1951</v>
       </c>
       <c r="N807" t="s">
-        <v>1999</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="808" spans="1:14" x14ac:dyDescent="0.25">
@@ -41939,7 +41991,7 @@
         <v>1</v>
       </c>
       <c r="B808" t="s">
-        <v>1992</v>
+        <v>1953</v>
       </c>
       <c r="D808">
         <v>0</v>
@@ -41948,22 +42000,22 @@
         <v>48</v>
       </c>
       <c r="F808" t="s">
-        <v>66</v>
+        <v>371</v>
       </c>
       <c r="G808" t="b">
         <v>0</v>
       </c>
       <c r="J808" t="s">
-        <v>1992</v>
+        <v>1948</v>
       </c>
       <c r="L808" t="s">
-        <v>1996</v>
+        <v>1954</v>
       </c>
       <c r="M808" t="s">
-        <v>2004</v>
+        <v>1955</v>
       </c>
       <c r="N808" t="s">
-        <v>2000</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="809" spans="1:14" x14ac:dyDescent="0.25">
@@ -41971,7 +42023,7 @@
         <v>1</v>
       </c>
       <c r="B809" t="s">
-        <v>1993</v>
+        <v>1957</v>
       </c>
       <c r="D809">
         <v>0</v>
@@ -41980,22 +42032,22 @@
         <v>48</v>
       </c>
       <c r="F809" t="s">
-        <v>66</v>
+        <v>371</v>
       </c>
       <c r="G809" t="b">
         <v>0</v>
       </c>
       <c r="J809" t="s">
-        <v>1993</v>
+        <v>1958</v>
       </c>
       <c r="L809" t="s">
-        <v>1997</v>
+        <v>1959</v>
       </c>
       <c r="M809" t="s">
-        <v>2005</v>
+        <v>1960</v>
       </c>
       <c r="N809" t="s">
-        <v>2001</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="810" spans="1:14" x14ac:dyDescent="0.25">
@@ -42003,7 +42055,7 @@
         <v>1</v>
       </c>
       <c r="B810" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="D810">
         <v>0</v>
@@ -42018,69 +42070,168 @@
         <v>0</v>
       </c>
       <c r="J810" t="s">
+        <v>1991</v>
+      </c>
+      <c r="L810" t="s">
+        <v>1995</v>
+      </c>
+      <c r="M810" t="s">
+        <v>2003</v>
+      </c>
+      <c r="N810" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="811" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>1</v>
+      </c>
+      <c r="B811" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D811">
+        <v>0</v>
+      </c>
+      <c r="E811" t="s">
+        <v>48</v>
+      </c>
+      <c r="F811" t="s">
+        <v>66</v>
+      </c>
+      <c r="G811" t="b">
+        <v>0</v>
+      </c>
+      <c r="J811" t="s">
+        <v>1992</v>
+      </c>
+      <c r="L811" t="s">
+        <v>1996</v>
+      </c>
+      <c r="M811" t="s">
+        <v>2004</v>
+      </c>
+      <c r="N811" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="812" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>1</v>
+      </c>
+      <c r="B812" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D812">
+        <v>0</v>
+      </c>
+      <c r="E812" t="s">
+        <v>48</v>
+      </c>
+      <c r="F812" t="s">
+        <v>66</v>
+      </c>
+      <c r="G812" t="b">
+        <v>0</v>
+      </c>
+      <c r="J812" t="s">
+        <v>1993</v>
+      </c>
+      <c r="L812" t="s">
+        <v>1997</v>
+      </c>
+      <c r="M812" t="s">
+        <v>2005</v>
+      </c>
+      <c r="N812" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="813" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>1</v>
+      </c>
+      <c r="B813" t="s">
         <v>1994</v>
       </c>
-      <c r="L810" t="s">
+      <c r="D813">
+        <v>0</v>
+      </c>
+      <c r="E813" t="s">
+        <v>48</v>
+      </c>
+      <c r="F813" t="s">
+        <v>66</v>
+      </c>
+      <c r="G813" t="b">
+        <v>0</v>
+      </c>
+      <c r="J813" t="s">
+        <v>1994</v>
+      </c>
+      <c r="L813" t="s">
         <v>1998</v>
       </c>
-      <c r="M810" t="s">
+      <c r="M813" t="s">
         <v>2006</v>
       </c>
-      <c r="N810" t="s">
+      <c r="N813" t="s">
         <v>2002</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B762:B810">
-    <cfRule type="duplicateValues" dxfId="16" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C756:C759 C762:C764">
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C766:C768">
-    <cfRule type="duplicateValues" dxfId="14" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C770:C772 C774:C776">
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J762:J773">
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J780:J781">
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J795:J797 J800">
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J798">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J799">
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J801:J802">
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J804">
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J805">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J807">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J808">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J810:J813">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P742:P754">
+    <cfRule type="duplicateValues" dxfId="4" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B762:B813">
+    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C770:C772 C774:C779">
+    <cfRule type="duplicateValues" dxfId="2" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J774:J776">
-    <cfRule type="duplicateValues" dxfId="11" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J777:J778">
-    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J792:J794 J797">
-    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J795">
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J796">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J798:J799">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J801">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J802">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J804">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J805">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J807:J810">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P742:P754">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  <conditionalFormatting sqref="J777:J779">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
